--- a/EndResult/50m Fri.xlsx
+++ b/EndResult/50m Fri.xlsx
@@ -1278,20 +1278,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25,97</t>
+          <t>25,67</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/EndResult/50m Fri.xlsx
+++ b/EndResult/50m Fri.xlsx
@@ -942,25 +942,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Erlend Tofte Haarsaker</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,99</t>
+          <t>24,87</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>07.07.2013</t>
+          <t>19.04.2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -977,25 +977,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Erlend Tofte Haarsaker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25,05</t>
+          <t>24,99</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28.05.2016</t>
+          <t>07.07.2013</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1012,20 +1012,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Leo Petter Hauge Sølvberg</t>
+          <t>Kristian Volden</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,06</t>
+          <t>25,05</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>07.04.2019</t>
+          <t>28.05.2016</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1047,20 +1047,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Leo Petter Hauge Sølvberg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,17</t>
+          <t>25,06</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>07.07.2024</t>
+          <t>07.04.2019</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1383,20 +1383,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27,00</t>
+          <t>26,95</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18.11.2023</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1518,25 +1518,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paulien Mulder</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27,62</t>
+          <t>27,59</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.11.2006</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1553,20 +1553,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Henriette Martinsen</t>
+          <t>Paulien Mulder</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27,65</t>
+          <t>27,62</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.11.2007</t>
+          <t>10.11.2006</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1588,25 +1588,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Renate Knutsen</t>
+          <t>Henriette Martinsen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27,68</t>
+          <t>27,65</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15.01.2023</t>
+          <t>10.11.2007</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1709,25 +1709,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tove Fludal Haugan</t>
+          <t>Silje Pettersen Olden</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27,27</t>
+          <t>27,24</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>08.07.2005</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1744,25 +1744,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Silje Pettersen Olden</t>
+          <t>Tove Fludal Haugan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27,53</t>
+          <t>27,27</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>04.07.2025</t>
+          <t>08.07.2005</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rud</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1884,25 +1884,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Henriette Martinsen</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,17</t>
+          <t>28,15</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.07.2008</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1919,25 +1919,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Henriette Martinsen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>28,50</t>
+          <t>28,17</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>11.07.2008</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1954,25 +1954,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sara Alonso Lopez</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,58</t>
+          <t>28,47</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.06.2021</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1989,25 +1989,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nora Kristine Rasmussen</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28,84</t>
+          <t>28,50</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.06.2015</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
